--- a/event_planner_forms/013_patronage_request_form--event_planner_forms.xlsx
+++ b/event_planner_forms/013_patronage_request_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sponsor_name</t>
+          <t>sponsor_name_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sponsor Name</t>
+          <t>Sponsor Name 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>submitter_email</t>
+          <t>submitter_email_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Submitter Email</t>
+          <t>Submitter Email 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>submitter_phone</t>
+          <t>submitter_phone_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Submitter Phone</t>
+          <t>Submitter Phone 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>submitter_agreement</t>
+          <t>submitter_agreement_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sponsor_agreement</t>
+          <t>sponsor_agreement_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sponsor Agreement</t>
+          <t>Sponsor Agreement 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>submitter_signature</t>
+          <t>submitter_signature_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sponsor_signature</t>
+          <t>sponsor_signature_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sponsor Signature</t>
+          <t>Sponsor Signature 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand_and_agree_to_the_terms_and_conditions.'}</t>
+          <t>i_understand_and_agree_to_the_terms_and_conditions.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'I understand and agree to the terms and conditions.'}</t>
+          <t>I understand and agree to the terms and conditions.</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'i_do_not_understand_and_do_not_agree_to_the_terms_and_conditions.'}</t>
+          <t>i_do_not_understand_and_do_not_agree_to_the_terms_and_conditions.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'I do not understand and do not agree to the terms and conditions.'}</t>
+          <t>I do not understand and do not agree to the terms and conditions.</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand_and_agree_to_the_terms_and_conditions.'}</t>
+          <t>i_understand_and_agree_to_the_terms_and_conditions.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'I understand and agree to the terms and conditions.'}</t>
+          <t>I understand and agree to the terms and conditions.</t>
         </is>
       </c>
     </row>
@@ -1182,80 +1182,80 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'i_do_not_understand_and_do_not_agree_to_the_terms_and_conditions.'}</t>
+          <t>i_do_not_understand_and_do_not_agree_to_the_terms_and_conditions.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'I do not understand and do not agree to the terms and conditions.'}</t>
+          <t>I do not understand and do not agree to the terms and conditions.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>submitter_agreement_choices</t>
+          <t>submitter_agreement_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand_and_agree_to_the_terms_and_conditions.'}</t>
+          <t>i_understand_and_agree_to_the_terms_and_conditions.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'I understand and agree to the terms and conditions.'}</t>
+          <t>I understand and agree to the terms and conditions.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>submitter_agreement_choices</t>
+          <t>submitter_agreement_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'i_do_not_understand_and_do_not_agree_to_the_terms_and_conditions.'}</t>
+          <t>i_do_not_understand_and_do_not_agree_to_the_terms_and_conditions.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'I do not understand and do not agree to the terms and conditions.'}</t>
+          <t>I do not understand and do not agree to the terms and conditions.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sponsor_agreement_choices</t>
+          <t>sponsor_agreement_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand_and_agree_to_the_terms_and_conditions.'}</t>
+          <t>i_understand_and_agree_to_the_terms_and_conditions.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'I understand and agree to the terms and conditions.'}</t>
+          <t>I understand and agree to the terms and conditions.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sponsor_agreement_choices</t>
+          <t>sponsor_agreement_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'i_do_not_understand_and_do_not_agree_to_the_terms_and_conditions.'}</t>
+          <t>i_do_not_understand_and_do_not_agree_to_the_terms_and_conditions.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'I do not understand and do not agree to the terms and conditions.'}</t>
+          <t>I do not understand and do not agree to the terms and conditions.</t>
         </is>
       </c>
     </row>
